--- a/artfynd/A 29038-2019 artfynd.xlsx
+++ b/artfynd/A 29038-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29038-2019 artfynd.xlsx
+++ b/artfynd/A 29038-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84127080</v>
+        <v>84127004</v>
       </c>
       <c r="B7" t="n">
         <v>96334</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316560.4428833294</v>
+        <v>316488.3080870484</v>
       </c>
       <c r="R7" t="n">
-        <v>6594051.837297586</v>
+        <v>6594058.405752056</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1469,132 +1469,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>84127004</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>S. Abborrtjärnen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>316488.3080870484</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6594058.405752056</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Årjäng</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Västra Fågelvik</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Bård E. Andersen</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Bård E. Andersen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
